--- a/examples/excel/charts/charts-bubble.xlsx
+++ b/examples/excel/charts/charts-bubble.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Bubble Fundamentals" sheetId="2" r:id="R28f9bfcf7ca4473c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Bubble Styling" sheetId="3" r:id="R47c62764b29e4fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Bubble Advanced" sheetId="4" r:id="Rfdeda35767a441c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Bubble Fundamentals" sheetId="2" r:id="R94e6de2e405548c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Bubble Styling" sheetId="3" r:id="R8651c580bff448c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Bubble Advanced" sheetId="4" r:id="Rb772f0f24c0946ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Bubble Series Data" sheetId="5" r:id="R20defc9ada9347a5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -697,6 +698,317 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/drawings/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>shownegbubbles — negative sizes visible</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:bubbleChart>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Data</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>90</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
+          <c:bubbleSize>
+            <c:numLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>90</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:bubbleSize>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Neg</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="C00000"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>70</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
+          <c:bubbleSize>
+            <c:numLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>70</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:bubbleSize>
+        </c:ser>
+        <c:bubbleScale val="80"/>
+        <c:showNegBubbles val="1"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:bubbleChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>series1.bubbleSize — range ref</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:bubbleChart>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Sizes</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="70AD47"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:xVal>
+            <c:numLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>80</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>60</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
+          <c:bubbleSize>
+            <c:numRef>
+              <c:f>4-Bubble Series Data!$A$1:$A$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:bubbleSize>
+        </c:ser>
+        <c:bubbleScale val="100"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:bubbleChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <c:chart>
@@ -1122,9 +1434,9 @@
           </c:bubbleSize>
         </c:ser>
         <c:bubbleScale val="100"/>
+        <c:sizeRepresents val="w"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
-        <c:sizeRepresents val="w"/>
       </c:bubbleChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -2040,8 +2352,7 @@
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:bubbleChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:bubbleChart>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
@@ -2108,7 +2419,7 @@
         </c:ser>
         <c:axId val="3"/>
         <c:axId val="4"/>
-      </c:lineChart>
+      </c:bubbleChart>
       <c:catAx>
         <c:axId val="1"/>
         <c:scaling>
@@ -2166,7 +2477,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -2206,7 +2517,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R291e60befff14245"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8669af0058894249"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2236,7 +2547,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R02fd40e60ad84cc0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R82e24ef50bed4ff6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2266,7 +2577,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re47419f4bac940d2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb2f6c0ff13df473b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2296,7 +2607,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb5cdc1f3a3c54dd7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7a9a0edcdb294a46"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2331,7 +2642,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R36e48436d4c7430f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra515e3a58ea643f2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2361,7 +2672,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9aa8d4da902249aa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R00177e7c834e4528"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2391,7 +2702,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rac945fec4b0e45ba"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf219012cd51443a5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2421,7 +2732,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1025233ce9d9453f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8609542f62824a8b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2456,7 +2767,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R585f5dd7175b409b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf7ec639841f0497b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2486,7 +2797,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4f16d1be04c1434b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R629be0847cf1462e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2516,7 +2827,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5a658621184e4722"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc3bf729d323944a7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2546,7 +2857,72 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d647762abcb4103"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5fdc2e203a794012"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="shownegbubbles — negative sizes visible"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6b78d3b8e6be4037"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="series1.bubbleSize — range ref"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R285cba787bb1454f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2558,20 +2934,43 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69c3b250e0234c87"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf035b1de3824a23"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15a25d6456c341d9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa5d5d48f1544356"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R375f312b12e340e2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re488b6e47efd4ece"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bdf3409c82245c1"/>
 </x:worksheet>
 </file>